--- a/Source/bcio_source.xlsx
+++ b/Source/bcio_source.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="007fffd4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002f4f4f"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,10 +60,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7057,56 +7063,56 @@
       <c r="Z110" s="2" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>BCIO:010086</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>school student role</t>
         </is>
       </c>
-      <c r="C111" s="2" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">A student or trainee that is currently learning at a primary or secondary education level in an institutional, organised setting. </t>
         </is>
       </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E111" s="2" t="n"/>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="2" t="n"/>
-      <c r="H111" s="2" t="n"/>
-      <c r="I111" s="2" t="n"/>
-      <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
-      <c r="L111" s="2" t="n"/>
-      <c r="M111" s="2" t="n"/>
-      <c r="N111" s="2" t="n"/>
-      <c r="O111" s="2" t="n"/>
-      <c r="P111" s="2" t="n"/>
-      <c r="Q111" s="2" t="n"/>
-      <c r="R111" s="2" t="n"/>
-      <c r="S111" s="2" t="n"/>
-      <c r="T111" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U111" s="2" t="n"/>
-      <c r="V111" s="2" t="n"/>
-      <c r="W111" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="X111" s="2" t="n"/>
-      <c r="Y111" s="2" t="n"/>
-      <c r="Z111" s="2" t="n"/>
+      <c r="E111" s="3" t="n"/>
+      <c r="F111" s="3" t="n"/>
+      <c r="G111" s="3" t="n"/>
+      <c r="H111" s="3" t="n"/>
+      <c r="I111" s="3" t="n"/>
+      <c r="J111" s="3" t="n"/>
+      <c r="K111" s="3" t="n"/>
+      <c r="L111" s="3" t="n"/>
+      <c r="M111" s="3" t="n"/>
+      <c r="N111" s="3" t="n"/>
+      <c r="O111" s="3" t="n"/>
+      <c r="P111" s="3" t="n"/>
+      <c r="Q111" s="3" t="n"/>
+      <c r="R111" s="3" t="n"/>
+      <c r="S111" s="3" t="n"/>
+      <c r="T111" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U111" s="3" t="n"/>
+      <c r="V111" s="3" t="n"/>
+      <c r="W111" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="X111" s="3" t="n"/>
+      <c r="Y111" s="3" t="n"/>
+      <c r="Z111" s="3" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -8926,56 +8932,56 @@
       <c r="Z141" s="2" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>BCIO:010087</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
+      <c r="B142" s="3" t="inlineStr">
         <is>
           <t>vocational training student or trainee role</t>
         </is>
       </c>
-      <c r="C142" s="2" t="inlineStr">
+      <c r="C142" s="3" t="inlineStr">
         <is>
           <t>A student or trainee role that is currently learning the curriculum material of vocational programme, normally in preparation for employment in a trade, job or profession.</t>
         </is>
       </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="D142" s="3" t="inlineStr">
         <is>
           <t>student or trainee role</t>
         </is>
       </c>
-      <c r="E142" s="2" t="n"/>
-      <c r="F142" s="2" t="n"/>
-      <c r="G142" s="2" t="n"/>
-      <c r="H142" s="2" t="n"/>
-      <c r="I142" s="2" t="n"/>
-      <c r="J142" s="2" t="n"/>
-      <c r="K142" s="2" t="n"/>
-      <c r="L142" s="2" t="n"/>
-      <c r="M142" s="2" t="n"/>
-      <c r="N142" s="2" t="n"/>
-      <c r="O142" s="2" t="n"/>
-      <c r="P142" s="2" t="n"/>
-      <c r="Q142" s="2" t="n"/>
-      <c r="R142" s="2" t="n"/>
-      <c r="S142" s="2" t="n"/>
-      <c r="T142" s="2" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="U142" s="2" t="n"/>
-      <c r="V142" s="2" t="n"/>
-      <c r="W142" s="2" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="X142" s="2" t="n"/>
-      <c r="Y142" s="2" t="n"/>
-      <c r="Z142" s="2" t="n"/>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
+      <c r="I142" s="3" t="n"/>
+      <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="n"/>
+      <c r="L142" s="3" t="n"/>
+      <c r="M142" s="3" t="n"/>
+      <c r="N142" s="3" t="n"/>
+      <c r="O142" s="3" t="n"/>
+      <c r="P142" s="3" t="n"/>
+      <c r="Q142" s="3" t="n"/>
+      <c r="R142" s="3" t="n"/>
+      <c r="S142" s="3" t="n"/>
+      <c r="T142" s="3" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="U142" s="3" t="n"/>
+      <c r="V142" s="3" t="n"/>
+      <c r="W142" s="3" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="X142" s="3" t="n"/>
+      <c r="Y142" s="3" t="n"/>
+      <c r="Z142" s="3" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
